--- a/rp/Excel/Task_任务表.xlsx
+++ b/rp/Excel/Task_任务表.xlsx
@@ -1272,7 +1272,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>

--- a/rp/Excel/Task_任务表.xlsx
+++ b/rp/Excel/Task_任务表.xlsx
@@ -842,13 +842,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1272,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
